--- a/flight_risk_employees.xlsx
+++ b/flight_risk_employees.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,13 +429,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>flight_risk_employee</t>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>negative_email_count</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>start_date</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>end_date</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>total_sentiment_score</t>
         </is>
       </c>
     </row>
@@ -441,19 +465,55 @@
           <t>john.arnold@enron.com</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>40335</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>40347</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>sally.beck@enron.com</t>
-        </is>
+          <t>patti.thompson@enron.com</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>40279</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>40300</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>patti.thompson@enron.com</t>
-        </is>
+          <t>sally.beck@enron.com</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>40352</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>40366</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-3</v>
       </c>
     </row>
   </sheetData>
